--- a/accountant-skill/data/Jan2026/financial_statements_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/financial_statements_Jan2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income Statement" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,13 +65,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF0000"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
       <sz val="11"/>
     </font>
     <font>
@@ -82,12 +83,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <i val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -110,7 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -162,25 +157,22 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -615,7 +607,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>7515000</v>
+        <v>7530000</v>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
@@ -627,7 +619,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>7515000</v>
+        <v>7530000</v>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
@@ -639,10 +631,10 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5194000</v>
+        <v>7530000</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.6912</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
     </row>
@@ -653,10 +645,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>456250</v>
+        <v>7530000</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.0607</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
     </row>
@@ -667,10 +659,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>462750</v>
+        <v>527750</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.0616</v>
+        <v>0.0701</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
     </row>
@@ -681,7 +673,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>13215750</v>
+        <v>12160750</v>
       </c>
       <c r="C12" s="6" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
@@ -705,7 +697,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>9142750</v>
+        <v>9207750</v>
       </c>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
@@ -747,12 +739,12 @@
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="C18" s="9" t="n">
+        <v>-1120000</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -764,11 +756,11 @@
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+        <v>527750</v>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -800,9 +792,7 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>1550000</v>
-      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
     </row>
@@ -812,8 +802,8 @@
           <t>Net Cash from Operations</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>-264500</v>
+      <c r="B24" s="7" t="n">
+        <v>527750</v>
       </c>
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
@@ -834,9 +824,7 @@
           <t>Net Cash from Financing</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
-        <v>300000</v>
-      </c>
+      <c r="B26" s="7" t="n"/>
       <c r="C26" s="6" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
     </row>
@@ -847,7 +835,7 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>35500</v>
+        <v>527750</v>
       </c>
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
@@ -858,18 +846,45 @@
           <t>Closing Cash Balance (per BS)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>1585500</v>
-      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="6" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
     </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>EXCEPTIONS &amp; WARNINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Balance Sheet does NOT balance: Assets=12,160,750.00, Equity+Liab=13,280,750.00, Diff=-1,120,000.00</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Cash Flow does NOT reconcile: Opening(0.00) + NetChange(527,750.00) != Closing(0.00), Diff=527,750.00</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -884,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -951,476 +966,360 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 1</t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1710000</v>
+        <v>7515000</v>
       </c>
       <c r="D7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 2</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2090000</v>
+        <v>15000</v>
       </c>
       <c r="D8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>4030</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Sales Revenue — Shop 3</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>1310000</v>
-      </c>
-      <c r="D9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Sales Revenue — General</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>2405000</v>
-      </c>
-      <c r="D10" s="7" t="n"/>
-    </row>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>NET REVENUE</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n">
+        <v>7530000</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>NET REVENUE</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n">
-        <v>7515000</v>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>COST OF GOODS SOLD</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL COGS</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+    </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>5010</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Raw Materials Used</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>2096000</v>
-      </c>
-      <c r="D14" s="7" t="n"/>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n">
+        <v>7530000</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>5020</t>
-        </is>
-      </c>
+      <c r="A15" s="6" t="inlineStr"/>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Packaging Costs</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="D15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL COGS</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="13" t="n">
-        <v>-2321000</v>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>Gross Profit Margin</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>GROSS PROFIT</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n">
-        <v>5194000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Gross Profit Margin</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="8" t="n">
-        <v>0.6912</v>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>OPERATING PROFIT</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n">
+        <v>7530000</v>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING EXPENSES</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>5100</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Salaries &amp; Wages</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>2755000</v>
-      </c>
-      <c r="D22" s="7" t="n"/>
-    </row>
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Operating Profit Margin</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>5110</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Employee Benefits</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D23" s="7" t="n"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>OTHER INCOME / (EXPENSES)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Rent Expense</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>1180000</v>
+          <t>Opening Inventory - Raw Materials</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>-2096000</v>
       </c>
       <c r="D24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Utilities Expense</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>125000</v>
+          <t>Opening Inventory - Packaging</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>-225000</v>
       </c>
       <c r="D25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>50310</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Telephone &amp; Internet</t>
+          <t>Closing Work-in-Progress</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73000</v>
+        <v>65000</v>
       </c>
       <c r="D26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>54750</v>
+          <t>Marketing &amp; Advertising Expense</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>-120000</v>
       </c>
       <c r="D27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Repairs &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>95000</v>
+          <t>Office Salaries</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>-2755000</v>
       </c>
       <c r="D28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>62000</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Cleaning &amp; Sanitation</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>45000</v>
+          <t>Meal Allowance Expense</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>-120000</v>
       </c>
       <c r="D29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>63000</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Transportation &amp; Delivery</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>85000</v>
+          <t>Utilities (Electricity &amp; Water)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>-125000</v>
       </c>
       <c r="D30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>64000</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>120000</v>
+          <t>Transportation &amp; Distribution Expense</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>-85000</v>
       </c>
       <c r="D31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Insurance Expense</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>85000</v>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>-1486500</v>
       </c>
       <c r="D32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="13" t="n">
-        <v>-4737750</v>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>OPERATING PROFIT</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n">
-        <v>456250</v>
-      </c>
-    </row>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>66000</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation Expenses - SG&amp;A</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>-54750</v>
+      </c>
+      <c r="D33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>NET OTHER INCOME/(EXPENSES)</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="15" t="n">
+        <v>-7002250</v>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Operating Profit Margin</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="8" t="n">
-        <v>0.0607</v>
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>PROFIT BEFORE TAX</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n">
+        <v>527750</v>
       </c>
     </row>
     <row r="37"/>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>OTHER INCOME / (EXPENSES)</t>
-        </is>
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>NET PROFIT / (LOSS)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n">
+        <v>527750</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>4110</t>
-        </is>
-      </c>
+      <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>5920</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Bank Charges &amp; Fees</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>-8500</v>
-      </c>
-      <c r="D40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>NET OTHER INCOME/(EXPENSES)</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>PROFIT BEFORE TAX</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="n"/>
-      <c r="C43" s="15" t="n"/>
-      <c r="D43" s="15" t="n">
-        <v>462750</v>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>NET PROFIT / (LOSS)</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="n"/>
-      <c r="C45" s="15" t="n"/>
-      <c r="D45" s="15" t="n">
-        <v>462750</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
           <t>Net Profit Margin</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="8" t="n">
-        <v>0.0616</v>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="8" t="n">
+        <v>0.0701</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1498,292 +1397,290 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>1610</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Buildings</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accumulated Depreciation — Buildings</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>-518750</v>
-      </c>
-      <c r="D8" s="7" t="n"/>
-    </row>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL NON-CURRENT ASSETS</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>1620</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Plant &amp; Machinery</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D9" s="7" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT ASSETS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accumulated Depreciation — Plant &amp; Machinery</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>-472500</v>
+          <t>Cash in hand</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>150000</v>
       </c>
       <c r="D10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Furniture &amp; Fixtures</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>800000</v>
+        <v>1435500</v>
       </c>
       <c r="D11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Account 1631</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>-166000</v>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>2605000</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Office Equipment</t>
+          <t>Inventory - Raw Material</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>500000</v>
+        <v>150000</v>
       </c>
       <c r="D13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accumulated Depreciation — Office Equipment</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>-107500</v>
+          <t>Inventory - Finished Goods</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>260000</v>
       </c>
       <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL NON-CURRENT ASSETS</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n">
-        <v>8035250</v>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>12400</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Work-in-Progress</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Payments</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D16" s="7" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT ASSETS</t>
-        </is>
-      </c>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>15100</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank — Main Account</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>1435500</v>
+          <t xml:space="preserve">  Accumulated Depreciation - Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>-518750</v>
       </c>
       <c r="D18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Petty Cash</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>150000</v>
+        <v>3000000</v>
       </c>
       <c r="D19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>3360000</v>
+          <t xml:space="preserve">  Accumulated Depreciation - Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>-472500</v>
       </c>
       <c r="D20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Allowance for Doubtful Debts</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>-15000</v>
+          <t>Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>500000</v>
       </c>
       <c r="D21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Inventory — Raw Materials</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>150000</v>
+          <t xml:space="preserve">  Accumulated Depreciation - Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>-113500</v>
       </c>
       <c r="D22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Prepaid Insurance</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>TOTAL CURRENT ASSETS</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n">
-        <v>5180500</v>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n">
+        <v>12160750</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n">
-        <v>13215750</v>
-      </c>
-    </row>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n">
+        <v>12160750</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27"/>
-    <row r="28"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>30200</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Account 30200</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="D29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Owner's Capital</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
@@ -1794,132 +1691,124 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Owner's Drawings</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>-200000</v>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>1200000</v>
       </c>
       <c r="D31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Current Period Net Profit/(Loss)</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>1200000</v>
+        <v>527750</v>
       </c>
       <c r="D32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Current Period Net Profit/(Loss)</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>462750</v>
-      </c>
-      <c r="D33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n">
-        <v>9142750</v>
-      </c>
-    </row>
-    <row r="35"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n">
+        <v>9207750</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>NON-CURRENT LIABILITIES</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>NON-CURRENT LIABILITIES</t>
-        </is>
-      </c>
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Long-term Loans</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>TOTAL NON-CURRENT LIABILITIES</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="39"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT LIABILITIES</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>CURRENT LIABILITIES</t>
-        </is>
-      </c>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1368000</v>
+      </c>
+      <c r="D40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>1368000</v>
+        <v>500000</v>
       </c>
       <c r="D41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Accrued Wages &amp; Salaries</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C42" s="7" t="n">
@@ -1930,16 +1819,16 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="D43" s="7" t="n"/>
     </row>
@@ -1952,7 +1841,7 @@
       <c r="B44" s="12" t="n"/>
       <c r="C44" s="12" t="n"/>
       <c r="D44" s="12" t="n">
-        <v>2073000</v>
+        <v>4073000</v>
       </c>
     </row>
     <row r="45"/>
@@ -1969,15 +1858,15 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>TOTAL EQUITY &amp; LIABILITIES</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="15" t="n">
-        <v>13215750</v>
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n">
+        <v>13280750</v>
       </c>
     </row>
     <row r="48"/>
@@ -1988,25 +1877,25 @@
           <t>CHECK: Assets - (Equity + Liabilities)</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="C49" s="9" t="n">
+        <v>-1120000</v>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2019,7 +1908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2091,263 +1980,213 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>462750</v>
+        <v>527750</v>
       </c>
       <c r="D7" s="7" t="n"/>
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Adjustments for non-cash items:</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Add: Depreciation</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>54750</v>
-      </c>
-      <c r="D10" s="7" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>NET CASH FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n">
+        <v>527750</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Changes in working capital:</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>No investing activities this period</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr"/>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Change in Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>-2560000</v>
-      </c>
-      <c r="D13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr"/>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Change in Allowance for Doubtful Debts</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="D14" s="7" t="n"/>
-    </row>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>NET CASH FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+    </row>
+    <row r="14"/>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Change in Inventory - Raw Materials</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D15" s="7" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Change in Prepaid Rent</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>20000</v>
-      </c>
+          <t>No financing activities this period</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Change in Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>1118000</v>
-      </c>
-      <c r="D17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Change in Accrued Wages</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>205000</v>
-      </c>
-      <c r="D18" s="7" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>NET CASH FROM OPERATING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="13" t="n">
-        <v>-264500</v>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>NET CASH FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>NET INCREASE/(DECREASE) IN CASH</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n">
+        <v>527750</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents at Start of Period</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="6" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>No investing activities this period</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-    </row>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents at End of Period</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+    </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>NET CASH FROM INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr"/>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Owner Capital Introduced</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr"/>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Owner Drawings</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>-200000</v>
-      </c>
-      <c r="D28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>NET CASH FROM FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>NET INCREASE/(DECREASE) IN CASH</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="15" t="n"/>
-      <c r="D31" s="15" t="n">
-        <v>35500</v>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Cash &amp; Cash Equivalents at Start of Period</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="D33" s="6" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Cash &amp; Cash Equivalents at End of Period</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="15" t="n"/>
-      <c r="D34" s="15" t="n">
-        <v>1585500</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>CHECK: Opening + Net Change - Closing =</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="C24" s="7" t="n">
+        <v>527750</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exceptions &amp; Warnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Financial Statements -- Module 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Exception / Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Balance Sheet does NOT balance: Assets=12,160,750.00, Equity+Liab=13,280,750.00, Diff=-1,120,000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Cash Flow does NOT reconcile: Opening(0.00) + NetChange(527,750.00) != Closing(0.00), Diff=527,750.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
